--- a/VerveStacks_UGA_grids_kan/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_UGA_grids_kan/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_UGA_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3A9E820D-F012-4E8F-80F5-62431D4BBF8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0A156C6C-0F97-44EA-A4BF-0E41E4A6DFE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="11" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -658,7 +658,7 @@
     <t>N</t>
   </si>
   <si>
-    <t>S01aH03,S01aH02,S01aH04</t>
+    <t>S01aH03,S01aH04,S01aH02</t>
   </si>
   <si>
     <t>H05</t>
@@ -667,7 +667,7 @@
     <t>S01aH05</t>
   </si>
   <si>
-    <t>S01aH02,S01aH03,S01aH04,S01aH05</t>
+    <t>S01aH03,S01aH02,S01aH04,S01aH05</t>
   </si>
   <si>
     <t>0101h01</t>
@@ -817,10 +817,10 @@
     <t>S01b0101h24</t>
   </si>
   <si>
-    <t>S01b0101h10,S01b0101h11,S01b0101h13,S01b0101h15,S01b0101h07,S01b0101h18,S01b0101h17,S01b0101h14,S01aH01,S01b0101h09,S01b0101h08,S01b0101h12,S01b0101h16</t>
+    <t>S01b0101h18,S01aH01,S01b0101h09,S01b0101h12,S01b0101h14,S01b0101h13,S01b0101h15,S01b0101h17,S01b0101h07,S01b0101h08,S01b0101h10,S01b0101h11,S01b0101h16</t>
   </si>
   <si>
-    <t>S01aH03,S01b0101h02,S01b0101h23,S01b0101h04,S01b0101h05,S01aH04,S01b0101h21,S01aH02,S01b0101h01,S01aH05,S01b0101h19,S01b0101h22,S01b0101h24,S01b0101h06,S01b0101h03,S01b0101h20</t>
+    <t>S01aH02,S01aH04,S01b0101h21,S01b0101h19,S01b0101h22,S01b0101h06,S01b0101h24,S01aH03,S01b0101h02,S01b0101h23,S01aH05,S01b0101h01,S01b0101h04,S01b0101h05,S01b0101h03,S01b0101h20</t>
   </si>
   <si>
     <t>c</t>
@@ -970,10 +970,10 @@
     <t>S01c0102h24</t>
   </si>
   <si>
-    <t>S01aH01,S01b0101h09,S01b0101h13,S01b0101h15,S01c0102h11,S01c0102h13,S01b0101h08,S01c0102h08,S01c0102h10,S01b0101h14,S01c0102h15,S01c0102h18,S01b0101h12,S01c0102h12,S01c0102h14,S01b0101h10,S01b0101h11,S01b0101h16,S01c0102h17,S01b0101h07,S01c0102h07,S01c0102h09,S01c0102h16,S01b0101h17,S01b0101h18</t>
+    <t>S01b0101h13,S01b0101h15,S01c0102h11,S01c0102h13,S01b0101h16,S01c0102h17,S01c0102h09,S01c0102h16,S01b0101h08,S01b0101h18,S01b0101h12,S01c0102h12,S01c0102h14,S01c0102h08,S01c0102h10,S01b0101h17,S01aH01,S01b0101h09,S01b0101h10,S01b0101h11,S01b0101h07,S01c0102h07,S01b0101h14,S01c0102h15,S01c0102h18</t>
   </si>
   <si>
-    <t>S01b0101h04,S01b0101h05,S01aH03,S01b0101h02,S01b0101h23,S01c0102h06,S01c0102h24,S01b0101h24,S01b0101h06,S01c0102h01,S01c0102h21,S01c0102h03,S01c0102h22,S01b0101h03,S01b0101h20,S01c0102h19,S01c0102h20,S01c0102h04,S01b0101h19,S01b0101h22,S01c0102h23,S01aH05,S01aH04,S01b0101h21,S01b0101h01,S01aH02,S01c0102h02,S01c0102h05</t>
+    <t>S01aH04,S01b0101h21,S01aH03,S01b0101h02,S01b0101h23,S01c0102h06,S01b0101h04,S01b0101h05,S01b0101h03,S01b0101h20,S01c0102h19,S01c0102h20,S01b0101h19,S01b0101h22,S01c0102h23,S01c0102h04,S01c0102h24,S01aH05,S01aH02,S01c0102h02,S01c0102h05,S01b0101h06,S01c0102h01,S01c0102h21,S01b0101h01,S01c0102h03,S01c0102h22,S01b0101h24</t>
   </si>
   <si>
     <t>AllS</t>
@@ -1039,10 +1039,10 @@
     <t>WaP</t>
   </si>
   <si>
-    <t>RaD,WaD,SaD,RaP,FaP,SaP,WaP,FaD</t>
+    <t>RaP,FaD,SaD,RaD,WaP,FaP,SaP,WaD</t>
   </si>
   <si>
-    <t>FaP,SaP,SaN,WaN,FaN,WaP,RaN,RaP</t>
+    <t>RaP,FaP,SaP,RaN,WaP,SaN,WaN,FaN</t>
   </si>
 </sst>
 </file>
@@ -9105,7 +9105,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9D272C4-6D8D-45EA-9CC0-2C583D7A0643}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84FA8539-7C92-498A-96A2-09AE5248DCD3}">
   <dimension ref="A9:AA911"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -29158,7 +29158,7 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{349275B4-3385-4978-A5B1-B7FD5DF14E26}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B243A98-554F-49D2-96F9-336F301B3105}">
   <dimension ref="A9:AA27"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -29647,7 +29647,7 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1E72E1A-0331-4348-8A94-0244847D6F60}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A2BB307-423E-4066-BBDD-1AB4EE9EE383}">
   <dimension ref="A9:AA214"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -49029,7 +49029,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A98BF72-C846-4087-8A47-D6C41C102BD5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEABF407-8A0B-481A-A101-AA9975E5C8A4}">
   <dimension ref="A9:G12"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -49094,7 +49094,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DAED14B-27C8-4909-9DAC-4E85958DC5AE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1353747-A577-4A76-994C-64A7E951A91F}">
   <dimension ref="A9:AA78"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -50711,7 +50711,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE6168B3-1DF3-497A-A89F-B661C7B2861C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66D677F7-C473-4B34-8D5B-0FB5FED2FDBC}">
   <dimension ref="A9:AA95"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -52704,7 +52704,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7322D930-4EBD-402E-AD0A-07C583D74658}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B27E8984-2441-49F3-99C5-EBE298B60DCC}">
   <dimension ref="A9:AA503"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
